--- a/core/api/export/templates/blanket_approval_details_template.xlsx
+++ b/core/api/export/templates/blanket_approval_details_template.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/david/Work/edw/ors-multilateralfund/core/api/export/templates/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288AC9A1-909E-764E-9007-253A0A133B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="2100" yWindow="1560" windowWidth="26420" windowHeight="16660" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects and activities" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Projects and activities" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,65 +27,65 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
-    <t xml:space="preserve">Project Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO2-eq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funds reccommended (US $)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(tonnes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">('000 tonnes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COUNTRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLUSTER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total for Armenia</t>
+    <t>Project Title</t>
+  </si>
+  <si>
+    <t>Agency</t>
+  </si>
+  <si>
+    <t>ODP</t>
+  </si>
+  <si>
+    <t>CO2-eq</t>
+  </si>
+  <si>
+    <t>(tonnes)</t>
+  </si>
+  <si>
+    <t>('000 tonnes)</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>COUNTRY</t>
+  </si>
+  <si>
+    <t>CLUSTER</t>
+  </si>
+  <si>
+    <t>TYPE</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Total for Armenia</t>
+  </si>
+  <si>
+    <t>Funds recommended (US$)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="_-\$* #,##0.00_-;&quot;-$&quot;* #,##0.00_-;_-\$* \-??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="\$#,##0;[RED]&quot;-$&quot;#,##0"/>
-    <numFmt numFmtId="167" formatCode="\$#,##0"/>
+    <numFmt numFmtId="164" formatCode="_-\$* #,##0.00_-;&quot;-$&quot;* #,##0.00_-;_-\$* \-??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="\$#,##0;[Red]&quot;-$&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="\$#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0;[Red]&quot;-$&quot;#,##0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,21 +94,6 @@
       <charset val="238"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -118,7 +108,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -126,7 +116,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -141,12 +131,19 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="3">
@@ -164,157 +161,120 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
-      <top style="medium"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="22">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellStyleXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="25">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="8">
+  <cellStyles count="3">
+    <cellStyle name="Currency 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Currency 2" xfId="20"/>
-    <cellStyle name="Normal 2" xfId="21"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -356,12 +316,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -393,7 +353,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -417,7 +377,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -477,81 +437,80 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="8.8046875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.85"/>
+    <col min="1" max="1" width="58.5" customWidth="1"/>
+    <col min="2" max="2" width="22.5" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" customWidth="1"/>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="7" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="19" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="9"/>
@@ -560,87 +519,87 @@
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1"/>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="13">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="21">
+        <v>0</v>
+      </c>
+      <c r="F7" s="21">
+        <v>0</v>
+      </c>
+      <c r="G7" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="2"/>
       <c r="C8" s="13"/>
       <c r="D8" s="11"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="15"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="16"/>
-      <c r="B9" s="1"/>
+      <c r="B9" s="2"/>
       <c r="C9" s="13"/>
       <c r="D9" s="11"/>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
       <c r="G9" s="15"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C10" s="17">
+        <v>0</v>
+      </c>
+      <c r="D10" s="17">
+        <v>0</v>
+      </c>
+      <c r="E10" s="23">
+        <v>0</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24">
         <v>0</v>
       </c>
     </row>
@@ -648,12 +607,7 @@
   <mergeCells count="1">
     <mergeCell ref="E2:G2"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/core/api/export/templates/blanket_approval_details_template.xlsx
+++ b/core/api/export/templates/blanket_approval_details_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/david/Work/edw/ors-multilateralfund/core/api/export/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288AC9A1-909E-764E-9007-253A0A133B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564EB7E8-7876-8A47-80FF-1F0C29E2BAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2100" yWindow="1560" windowWidth="26420" windowHeight="16660" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -192,11 +192,8 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -253,6 +250,24 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -453,159 +468,158 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58.5" customWidth="1"/>
-    <col min="2" max="2" width="22.5" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" customWidth="1"/>
+    <col min="2" max="4" width="10.1640625" customWidth="1"/>
     <col min="5" max="5" width="10.5" customWidth="1"/>
     <col min="6" max="6" width="11.1640625" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+    <row r="1" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6" t="s">
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+    </row>
+    <row r="3" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="13">
-        <v>0</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="21">
-        <v>0</v>
-      </c>
-      <c r="F7" s="21">
-        <v>0</v>
-      </c>
-      <c r="G7" s="22">
+      <c r="C7" s="25">
+        <v>0</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="E7" s="20">
+        <v>0</v>
+      </c>
+      <c r="F7" s="20">
+        <v>0</v>
+      </c>
+      <c r="G7" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="15"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="14"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="16"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="17">
-        <v>0</v>
-      </c>
-      <c r="D10" s="17">
-        <v>0</v>
-      </c>
-      <c r="E10" s="23">
-        <v>0</v>
-      </c>
-      <c r="F10" s="23">
-        <v>0</v>
-      </c>
-      <c r="G10" s="24">
+      <c r="B10" s="28"/>
+      <c r="C10" s="16">
+        <v>0</v>
+      </c>
+      <c r="D10" s="16">
+        <v>0</v>
+      </c>
+      <c r="E10" s="22">
+        <v>0</v>
+      </c>
+      <c r="F10" s="22">
+        <v>0</v>
+      </c>
+      <c r="G10" s="23">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/core/api/export/templates/blanket_approval_details_template.xlsx
+++ b/core/api/export/templates/blanket_approval_details_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/david/Work/edw/ors-multilateralfund/core/api/export/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564EB7E8-7876-8A47-80FF-1F0C29E2BAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECBEFA7-2DE5-6347-A289-D7D39E84480B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2100" yWindow="1560" windowWidth="26420" windowHeight="16660" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -251,23 +251,23 @@
     <xf numFmtId="3" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -464,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A2:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58.5" customWidth="1"/>
@@ -474,78 +474,67 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="29" t="s">
+    <row r="2" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E3" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-    </row>
-    <row r="3" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5" t="s">
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+    </row>
+    <row r="4" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="26" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="10"/>
@@ -555,39 +544,41 @@
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B8" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="25">
-        <v>0</v>
-      </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="20">
-        <v>0</v>
-      </c>
-      <c r="F7" s="20">
-        <v>0</v>
-      </c>
-      <c r="G7" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
+      <c r="C8" s="24">
+        <v>0</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="20">
+        <v>0</v>
+      </c>
+      <c r="F8" s="20">
+        <v>0</v>
+      </c>
+      <c r="G8" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="14"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="15"/>
       <c r="B9" s="1"/>
       <c r="C9" s="12"/>
       <c r="D9" s="10"/>
@@ -596,30 +587,39 @@
       <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="15"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="16">
-        <v>0</v>
-      </c>
-      <c r="D10" s="16">
-        <v>0</v>
-      </c>
-      <c r="E10" s="22">
-        <v>0</v>
-      </c>
-      <c r="F10" s="22">
-        <v>0</v>
-      </c>
-      <c r="G10" s="23">
+      <c r="B11" s="29"/>
+      <c r="C11" s="16">
+        <v>0</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0</v>
+      </c>
+      <c r="E11" s="22">
+        <v>0</v>
+      </c>
+      <c r="F11" s="22">
+        <v>0</v>
+      </c>
+      <c r="G11" s="23">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A11:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
